--- a/artfynd/A 51910-2024 artfynd.xlsx
+++ b/artfynd/A 51910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90655440</v>
+        <v>86826471</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,25 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyhem: Väg Z 323, Jmt</t>
+          <t>Muskaråsen, Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539677.9977544481</v>
+        <v>539724</v>
       </c>
       <c r="R2" t="n">
-        <v>6982181.187489009</v>
+        <v>6982175</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +746,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-26</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-26</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>enstaka</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,23 +773,125 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>90655440</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nyhem: Väg Z 323, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>539678</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6982181</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-06-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Leif Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Jonny Daborg, Fredrik Larsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
